--- a/BVSimulationFiles/87.xlsx
+++ b/BVSimulationFiles/87.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0001673151750972763</v>
+        <v>0.0003346303501945526</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001943477370468974</v>
+        <v>0.0003886954740937948</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002213802989965185</v>
+        <v>0.000442760597993037</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002484128609461397</v>
+        <v>0.0004968257218922794</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002754454228957608</v>
+        <v>0.0005508908457915216</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003024779848453819</v>
+        <v>0.0006049559696907638</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000329510546795003</v>
+        <v>0.0006590210935900059</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003565431087446242</v>
+        <v>0.0007130862174892484</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003835756706942453</v>
+        <v>0.0007671513413884906</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004106082326438665</v>
+        <v>0.000821216465287733</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004376407945934876</v>
+        <v>0.0008752815891869752</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0004646733565431087</v>
+        <v>0.0009293467130862174</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0004917059184927298</v>
+        <v>0.0009834118369854597</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000518738480442351</v>
+        <v>0.001037476960884702</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0005457710423919721</v>
+        <v>0.001091542084783944</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0005728036043415932</v>
+        <v>0.001145607208683186</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0005998361662912144</v>
+        <v>0.001199672332582429</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0006268687282408355</v>
+        <v>0.001253737456481671</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0006539012901904568</v>
+        <v>0.001307802580380914</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0006809338521400778</v>
+        <v>0.001361867704280156</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0001673151750972763</v>
+        <v>0.0003346303501945526</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0001943477370468974</v>
+        <v>0.0003886954740937948</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002213802989965185</v>
+        <v>0.000442760597993037</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0002484128609461397</v>
+        <v>0.0004968257218922794</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0002754454228957608</v>
+        <v>0.0005508908457915216</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0003024779848453819</v>
+        <v>0.0006049559696907638</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000329510546795003</v>
+        <v>0.0006590210935900059</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0003565431087446242</v>
+        <v>0.0007130862174892484</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003835756706942453</v>
+        <v>0.0007671513413884906</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004106082326438665</v>
+        <v>0.000821216465287733</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004376407945934876</v>
+        <v>0.0008752815891869752</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0004646733565431087</v>
+        <v>0.0009293467130862174</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0004917059184927298</v>
+        <v>0.0009834118369854597</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000518738480442351</v>
+        <v>0.001037476960884702</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0005457710423919721</v>
+        <v>0.001091542084783944</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0005728036043415932</v>
+        <v>0.001145607208683186</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0005998361662912144</v>
+        <v>0.001199672332582429</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0006268687282408355</v>
+        <v>0.001253737456481671</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0006539012901904568</v>
+        <v>0.001307802580380914</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0006809338521400778</v>
+        <v>0.001361867704280156</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/87.xlsx
+++ b/BVSimulationFiles/87.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0003346303501945526</v>
+        <v>0.003346303501945526</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0003886954740937948</v>
+        <v>0.003886954740937948</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000442760597993037</v>
+        <v>0.00442760597993037</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0004968257218922794</v>
+        <v>0.004968257218922793</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0005508908457915216</v>
+        <v>0.005508908457915216</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0006049559696907638</v>
+        <v>0.006049559696907638</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0006590210935900059</v>
+        <v>0.00659021093590006</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007130862174892484</v>
+        <v>0.007130862174892484</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007671513413884906</v>
+        <v>0.007671513413884906</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000821216465287733</v>
+        <v>0.00821216465287733</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008752815891869752</v>
+        <v>0.008752815891869752</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0009293467130862174</v>
+        <v>0.009293467130862175</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0009834118369854597</v>
+        <v>0.009834118369854598</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001037476960884702</v>
+        <v>0.01037476960884702</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001091542084783944</v>
+        <v>0.01091542084783944</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001145607208683186</v>
+        <v>0.01145607208683186</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001199672332582429</v>
+        <v>0.01199672332582429</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001253737456481671</v>
+        <v>0.01253737456481671</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001307802580380914</v>
+        <v>0.01307802580380914</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001361867704280156</v>
+        <v>0.01361867704280156</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0003346303501945526</v>
+        <v>0.003346303501945526</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0003886954740937948</v>
+        <v>0.003886954740937948</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000442760597993037</v>
+        <v>0.00442760597993037</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004968257218922794</v>
+        <v>0.004968257218922793</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005508908457915216</v>
+        <v>0.005508908457915216</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006049559696907638</v>
+        <v>0.006049559696907638</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0006590210935900059</v>
+        <v>0.00659021093590006</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007130862174892484</v>
+        <v>0.007130862174892484</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007671513413884906</v>
+        <v>0.007671513413884906</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000821216465287733</v>
+        <v>0.00821216465287733</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008752815891869752</v>
+        <v>0.008752815891869752</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0009293467130862174</v>
+        <v>0.009293467130862175</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0009834118369854597</v>
+        <v>0.009834118369854598</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001037476960884702</v>
+        <v>0.01037476960884702</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001091542084783944</v>
+        <v>0.01091542084783944</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001145607208683186</v>
+        <v>0.01145607208683186</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001199672332582429</v>
+        <v>0.01199672332582429</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001253737456481671</v>
+        <v>0.01253737456481671</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001307802580380914</v>
+        <v>0.01307802580380914</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001361867704280156</v>
+        <v>0.01361867704280156</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/87.xlsx
+++ b/BVSimulationFiles/87.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,60 +421,90 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.002817894736842105</v>
+        <v>0.001846206896551724</v>
       </c>
       <c r="D1" t="n">
-        <v>0.00563578947368421</v>
+        <v>0.003692413793103448</v>
       </c>
       <c r="E1" t="n">
-        <v>0.008453684210526315</v>
+        <v>0.005538620689655173</v>
       </c>
       <c r="F1" t="n">
-        <v>0.01127157894736842</v>
+        <v>0.007384827586206896</v>
       </c>
       <c r="G1" t="n">
-        <v>0.01408947368421053</v>
+        <v>0.00923103448275862</v>
       </c>
       <c r="H1" t="n">
-        <v>0.01690736842105263</v>
+        <v>0.01107724137931035</v>
       </c>
       <c r="I1" t="n">
-        <v>0.01972526315789474</v>
+        <v>0.01292344827586207</v>
       </c>
       <c r="J1" t="n">
-        <v>0.02254315789473684</v>
+        <v>0.01476965517241379</v>
       </c>
       <c r="K1" t="n">
-        <v>0.02536105263157895</v>
+        <v>0.01661586206896552</v>
       </c>
       <c r="L1" t="n">
-        <v>0.02817894736842105</v>
+        <v>0.01846206896551724</v>
       </c>
       <c r="M1" t="n">
-        <v>0.03099684210526316</v>
+        <v>0.02030827586206897</v>
       </c>
       <c r="N1" t="n">
-        <v>0.03381473684210526</v>
+        <v>0.02215448275862069</v>
       </c>
       <c r="O1" t="n">
-        <v>0.03663263157894737</v>
+        <v>0.02400068965517241</v>
       </c>
       <c r="P1" t="n">
-        <v>0.03945052631578947</v>
+        <v>0.02584689655172414</v>
       </c>
       <c r="Q1" t="n">
-        <v>0.04226842105263158</v>
+        <v>0.02769310344827586</v>
       </c>
       <c r="R1" t="n">
-        <v>0.04508631578947368</v>
+        <v>0.02953931034482759</v>
       </c>
       <c r="S1" t="n">
-        <v>0.04790421052631579</v>
+        <v>0.03138551724137931</v>
       </c>
       <c r="T1" t="n">
-        <v>0.05072210526315789</v>
+        <v>0.03323172413793103</v>
       </c>
       <c r="U1" t="n">
+        <v>0.03507793103448276</v>
+      </c>
+      <c r="V1" t="n">
+        <v>0.03692413793103448</v>
+      </c>
+      <c r="W1" t="n">
+        <v>0.03877034482758621</v>
+      </c>
+      <c r="X1" t="n">
+        <v>0.04061655172413794</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>0.04246275862068966</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>0.04430896551724138</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>0.04615517241379311</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>0.04800137931034483</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>0.04984758620689655</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>0.05169379310344828</v>
+      </c>
+      <c r="AE1" t="n">
         <v>0.05354</v>
       </c>
     </row>
@@ -483,64 +513,94 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.003346303501945526</v>
+        <v>0.02072298612530545</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003886954740937948</v>
+        <v>0.02291659812894645</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00442760597993037</v>
+        <v>0.02511021013258744</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004968257218922793</v>
+        <v>0.02730382213622844</v>
       </c>
       <c r="F2" t="n">
-        <v>0.005508908457915216</v>
+        <v>0.02949743413986943</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006049559696907638</v>
+        <v>0.03169104614351043</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00659021093590006</v>
+        <v>0.03388465814715141</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007130862174892484</v>
+        <v>0.03607827015079242</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007671513413884906</v>
+        <v>0.0382718821544334</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00821216465287733</v>
+        <v>0.0404654941580744</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008752815891869752</v>
+        <v>0.04265910616171539</v>
       </c>
       <c r="M2" t="n">
-        <v>0.009293467130862175</v>
+        <v>0.04485271816535639</v>
       </c>
       <c r="N2" t="n">
-        <v>0.009834118369854598</v>
+        <v>0.04704633016899739</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01037476960884702</v>
+        <v>0.04923994217263838</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01091542084783944</v>
+        <v>0.05143355417627937</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01145607208683186</v>
+        <v>0.05362716617992037</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01199672332582429</v>
+        <v>0.05582077818356137</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01253737456481671</v>
+        <v>0.05801439018720236</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01307802580380914</v>
+        <v>0.06020800219084335</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01361867704280156</v>
+        <v>0.06240161419448435</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.06459522619812534</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.06678883820176633</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.06898245020540733</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.07117606220904832</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.07336967421268931</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.07556328621633031</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.07775689821997131</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.0799505102236123</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.08214412222725329</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.08433773423089429</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +608,94 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.003346303501945526</v>
+        <v>0.02072298612530545</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003886954740937948</v>
+        <v>0.02291659812894645</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00442760597993037</v>
+        <v>0.02511021013258744</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004968257218922793</v>
+        <v>0.02730382213622844</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005508908457915216</v>
+        <v>0.02949743413986943</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006049559696907638</v>
+        <v>0.03169104614351043</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00659021093590006</v>
+        <v>0.03388465814715141</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007130862174892484</v>
+        <v>0.03607827015079242</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007671513413884906</v>
+        <v>0.0382718821544334</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00821216465287733</v>
+        <v>0.0404654941580744</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008752815891869752</v>
+        <v>0.04265910616171539</v>
       </c>
       <c r="M3" t="n">
-        <v>0.009293467130862175</v>
+        <v>0.04485271816535639</v>
       </c>
       <c r="N3" t="n">
-        <v>0.009834118369854598</v>
+        <v>0.04704633016899739</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01037476960884702</v>
+        <v>0.04923994217263838</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01091542084783944</v>
+        <v>0.05143355417627937</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01145607208683186</v>
+        <v>0.05362716617992037</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01199672332582429</v>
+        <v>0.05582077818356137</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01253737456481671</v>
+        <v>0.05801439018720236</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01307802580380914</v>
+        <v>0.06020800219084335</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01361867704280156</v>
+        <v>0.06240161419448435</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.06459522619812534</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.06678883820176633</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.06898245020540733</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.07117606220904832</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.07336967421268931</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.07556328621633031</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.07775689821997131</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.0799505102236123</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.08214412222725329</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.08433773423089429</v>
       </c>
     </row>
   </sheetData>
